--- a/output/pdf_financials_xlsx/CAPL.P.xlsx
+++ b/output/pdf_financials_xlsx/CAPL.P.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,25 +447,30 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2023-01</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>2024-01</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
@@ -484,30 +489,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -516,30 +514,23 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -548,30 +539,23 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,30 +564,23 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.003055</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.002559</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.013306</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.015487</v>
       </c>
     </row>
     <row r="8">
@@ -612,30 +589,23 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -644,30 +614,23 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -676,30 +639,23 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.003055</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.002559</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.013306</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.015487</v>
       </c>
     </row>
     <row r="11">
@@ -708,30 +664,23 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.003055</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.136093</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.06454500000000001</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.013306</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-0.015487</v>
       </c>
     </row>
     <row r="12">
@@ -740,30 +689,23 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -772,30 +714,23 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -804,30 +739,23 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -836,30 +764,23 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -868,30 +789,23 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-0.083716</v>
       </c>
     </row>
     <row r="17">
@@ -900,30 +814,23 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -957,6 +864,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -989,6 +901,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -996,30 +913,23 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-0.083716</v>
       </c>
     </row>
     <row r="21">
@@ -1028,30 +938,23 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1060,30 +963,23 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1092,30 +988,23 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-0.083716</v>
       </c>
     </row>
     <row r="24">
@@ -1134,20 +1023,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="25">
@@ -1166,20 +1052,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -1198,10 +1081,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>6.82945</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1209,6 +1090,11 @@
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1220,30 +1106,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.083716</v>
       </c>
     </row>
     <row r="28">
@@ -1252,30 +1131,23 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1284,30 +1156,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-0.083716</v>
       </c>
     </row>
     <row r="30">
@@ -1341,6 +1206,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1348,30 +1218,23 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1405,6 +1268,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1424,25 +1292,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1456,25 +1319,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1488,25 +1346,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1520,25 +1373,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1552,25 +1400,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1584,25 +1427,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1616,25 +1454,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1643,28 +1476,25 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>1e-06</v>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1678,25 +1508,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1710,25 +1535,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1742,25 +1562,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1774,25 +1589,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1806,25 +1616,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1838,25 +1643,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1870,25 +1670,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>0.281751</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.344996</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1902,15 +1697,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="3" t="n">
+        <v>0.281752</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.344996</v>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
@@ -1918,6 +1709,11 @@
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1934,25 +1730,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1966,25 +1757,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1998,25 +1784,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2030,25 +1811,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2062,25 +1838,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2114,6 +1885,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2126,25 +1902,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2158,25 +1929,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2190,25 +1956,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2222,25 +1983,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2254,25 +2010,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2286,25 +2037,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2338,6 +2084,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2370,6 +2121,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2382,25 +2138,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2414,25 +2165,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2446,25 +2192,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2478,25 +2219,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2505,19 +2241,24 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>0.004452</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>0.021945</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>0.022266</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="F68" s="3" t="n">
         <v>0.020894</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="G68" s="3" t="n">
         <v>0.024262</v>
       </c>
     </row>
@@ -2532,25 +2273,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2564,25 +2300,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2596,25 +2327,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2628,25 +2354,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2660,25 +2381,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2692,25 +2408,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2724,25 +2435,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2776,6 +2482,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -2788,25 +2499,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2820,25 +2526,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2852,25 +2553,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2904,6 +2600,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -2916,25 +2617,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2948,25 +2644,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2980,25 +2671,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3012,25 +2698,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3044,25 +2725,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3096,6 +2772,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -3128,6 +2809,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -3140,25 +2826,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>0.300001</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.389947</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.389947</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.407486</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.407486</v>
       </c>
     </row>
     <row r="89">
@@ -3172,25 +2853,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3199,19 +2875,24 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>-0.022701</v>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="D90" s="3" t="n">
         <v>-0.15929</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="E90" s="3" t="n">
         <v>-0.224359</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="F90" s="3" t="n">
         <v>-0.289167</v>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="G90" s="3" t="n">
         <v>-0.365345</v>
       </c>
     </row>
@@ -3226,25 +2907,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3258,25 +2934,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3290,25 +2961,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3322,25 +2988,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C94" s="3" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.323051</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.257982</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.203174</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.119458</v>
       </c>
     </row>
     <row r="95">
@@ -3354,25 +3015,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3386,25 +3042,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.323051</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.257982</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.203174</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0.119458</v>
       </c>
     </row>
     <row r="97">
@@ -3438,6 +3089,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3457,25 +3113,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.022701</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-0.083716</v>
       </c>
     </row>
     <row r="100">
@@ -3489,25 +3140,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3521,25 +3167,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3553,25 +3194,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3585,25 +3221,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3612,19 +3243,24 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="3" t="n">
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
         <v>0.004452</v>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="D104" s="3" t="n">
         <v>0.017493</v>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="E104" s="3" t="n">
         <v>0.000321</v>
       </c>
-      <c r="E104" s="3" t="n">
+      <c r="F104" s="3" t="n">
         <v>-0.001372</v>
       </c>
-      <c r="F104" s="3" t="n">
+      <c r="G104" s="3" t="n">
         <v>0.003368</v>
       </c>
     </row>
@@ -3639,25 +3275,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3671,25 +3302,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>-0.02425</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.035778</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.064748</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.06618</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-0.080348</v>
       </c>
     </row>
     <row r="107">
@@ -3704,22 +3330,19 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
         <v>0.077317</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3733,25 +3356,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3765,25 +3383,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3797,25 +3410,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3829,25 +3437,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3861,25 +3464,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3893,25 +3491,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3925,25 +3518,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3957,25 +3545,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3989,25 +3572,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4021,25 +3599,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4053,25 +3626,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4105,6 +3673,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -4117,25 +3690,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4149,25 +3717,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4181,25 +3744,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4213,25 +3771,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4245,25 +3798,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4277,25 +3825,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4309,25 +3852,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4361,6 +3899,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -4373,25 +3916,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0.105023</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4425,6 +3963,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -4438,15 +3981,18 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="n">
         <v>0.275751</v>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="E130" s="3" t="n">
         <v>0.344996</v>
       </c>
-      <c r="E130" s="3" t="n">
+      <c r="F130" s="3" t="n">
         <v>0.280248</v>
       </c>
-      <c r="F130" s="3" t="n">
+      <c r="G130" s="3" t="n">
         <v>0.224068</v>
       </c>
     </row>
@@ -4461,25 +4007,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4493,25 +4034,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>0.275751</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.069245</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.064748</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.05618</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>-0.080348</v>
       </c>
     </row>
     <row r="133">
@@ -4520,19 +4056,24 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="3" t="n">
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
         <v>0.275751</v>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="D133" s="3" t="n">
         <v>0.344996</v>
       </c>
-      <c r="D133" s="3" t="n">
+      <c r="E133" s="3" t="n">
         <v>0.280248</v>
       </c>
-      <c r="E133" s="3" t="n">
+      <c r="F133" s="3" t="n">
         <v>0.224068</v>
       </c>
-      <c r="F133" s="3" t="n">
+      <c r="G133" s="3" t="n">
         <v>0.14372</v>
       </c>
     </row>
@@ -4547,25 +4088,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4595,6 +4131,11 @@
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4611,7 +4152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4643,25 +4184,30 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -4688,19 +4234,24 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>0.275751</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="5" t="n">
         <v>0.344996</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="H2" s="5" t="n">
         <v>0.280248</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="I2" s="5" t="n">
         <v>0.224068</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>0.14372</v>
       </c>
     </row>
@@ -4735,13 +4286,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>0.022266</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>0.020894</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.024262</v>
       </c>
     </row>
@@ -4766,21 +4322,26 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>0.300001</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.389947</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.389947</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.407486</v>
+        <v>0.389947</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0.407486</v>
       </c>
+      <c r="J4" s="5" t="n">
+        <v>0.407486</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4804,16 +4365,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>0.092394</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.092394</v>
       </c>
       <c r="H5" s="5" t="n">
+        <v>0.092394</v>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>0.084855</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0.077317</v>
       </c>
     </row>
@@ -4838,19 +4404,24 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>-0.022701</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>-0.15929</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>-0.224359</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>-0.289167</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>-0.365345</v>
       </c>
     </row>
@@ -4870,20 +4441,29 @@
           <t>Shareholders’ equity total</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="5" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>0.2773</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>0.323051</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.257982</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>0.203174</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>0.119458</v>
       </c>
     </row>
@@ -4908,21 +4488,26 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>0.004452</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.021945</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>0.022266</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4949,14 +4534,14 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>1e-06</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4968,6 +4553,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4990,14 +4580,14 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" s="5" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>0.006</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5009,6 +4599,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5030,24 +4625,33 @@
           <t>Current total</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>0.281752</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>0.344996</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5069,22 +4673,31 @@
           <t>Net loss</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>-0.136589</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>-0.065069</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>-0.064808</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>-0.083716</v>
       </c>
     </row>
@@ -5109,19 +4722,24 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>0.004452</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.017493</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>0.000321</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>-0.001372</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>0.003368</v>
       </c>
     </row>
@@ -5141,20 +4759,29 @@
           <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="5" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>-0.02425</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>-0.035778</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>-0.064748</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>-0.06618</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="J14" s="5" t="n">
         <v>-0.080348</v>
       </c>
     </row>
@@ -5174,24 +4801,33 @@
           <t>Shares issued for cash, net of share issue costs</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>0.105023</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5213,7 +4849,11 @@
           <t>Decrease in cash</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5224,13 +4864,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>-0.064748</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>-0.05618</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>-0.080348</v>
       </c>
     </row>
@@ -5260,16 +4905,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>0.275751</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>0.344996</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.280248</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>0.224068</v>
       </c>
     </row>
@@ -5294,19 +4944,24 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>0.275751</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>0.344996</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>0.280248</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>0.224068</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>0.14372</v>
       </c>
     </row>
@@ -5336,20 +4991,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>0.077317</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5371,24 +5031,33 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" s="5" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>1e-06</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5410,24 +5079,33 @@
           <t>Prepaids expenses</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" s="5" t="n">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>-0.006</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="G21" s="5" t="n">
         <v>0.006</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5449,24 +5127,33 @@
           <t>(Decrease) Increase in cash</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>0.069245</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>-0.064748</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5488,24 +5175,33 @@
           <t>Net loss for the period</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>-0.022701</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>-0.136589</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5528,23 +5224,28 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>0.300001</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="G24" s="5" t="n">
         <v>0.105023</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5566,24 +5267,1669 @@
           <t>Increase in cash</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>0.275751</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="G25" s="5" t="n">
         <v>0.069245</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Office and general 5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.003055</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0.013306</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.015487</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.035078</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0.033852</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.050963</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Regulatory and transfer agent</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.018003</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.016831</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0.017266</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-0.083716</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Net loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>8.0001</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>8.071607</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>8.100099999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2025 8,100,100 407,486 77,317 7,538 84,855</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0.203174</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.203174</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-0.289167</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Expired broker warrants 4(c) - - - (7,538) (7,538)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0.007538</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Net loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>-0.064808</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.083716</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-0.083716</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2026 8,100,100 407,486 77,317 - 77,317</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.119458</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>-0.365345</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2024 8,000,100 389,947 77,317 15,077 92,394</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.257982</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.257982</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.257982</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.224359</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Exercise of broker warrants 4(b) 100,000 17,539 - (7,539) (7,539)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2023 8,000,100 389,947 77,317 15,077 92,394</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.323051</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.323051</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>-0.15929</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Professional fees 5</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.037718</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.035078</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Share-based compensation 4(d)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.077317</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.136093</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>-0.06454500000000001</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.000496</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>-0.0005240000000000001</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>-0.065069</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Net loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>6.487771</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>8.0001</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2022 6,000,100 300,001 - - -</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>-0.022701</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IPO shares issued 4(b) 2,000,000 200,000 - - -</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Share issuance costs 4(b) - (110,054) - 15,077 15,077</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.09497700000000001</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Share-based compensation 4(d) - - 77,317 - 77,317</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.077317</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Listing fees 15,750 -</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.003055</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Listing fees 15,750 -</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.037718</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.014608</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2022 6,000,100 300,001 - -</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>-0.022701</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>IPO shares issued 4(b) 2,000,000 200,000 - -</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (110,054) - 15,077</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-0.09497700000000001</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.015077</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 77,317 -</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.077317</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.077317</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.136589</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2023 8,000,100 389,947 77,317 15,077</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>-0.15929</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.323051</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.092394</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Balance, March 29, 2021 - - - -</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Incorporation shares 100 1 - -</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Private placement 4(b) 6,000,000 300,000 - -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Net loss for the period - - - -</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>-0.022701</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-0.022701</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/CAPL.P.xlsx
+++ b/output/pdf_financials_xlsx/CAPL.P.xlsx
@@ -431,6 +431,15 @@
   </sheetPr>
   <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAPL.P.xlsx
+++ b/output/pdf_financials_xlsx/CAPL.P.xlsx
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.002559</v>
+        <v>0.003551</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.01316</v>
@@ -630,16 +630,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.018003</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.016831</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.01765</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.017266</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.002559</v>
+        <v>0.021554</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.01316</v>
+        <v>0.029991</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.013306</v>
+        <v>0.030956</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.015487</v>
+        <v>0.032753</v>
       </c>
     </row>
     <row r="11">
@@ -686,10 +686,10 @@
         <v>-0.06454500000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.013306</v>
+        <v>-0.030956</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.015487</v>
+        <v>-0.032753</v>
       </c>
     </row>
     <row r="12">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -3117,13 +3117,13 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n">
+      <c r="B99" s="3" t="n">
         <v>-0.022701</v>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.136589</v>
@@ -3144,13 +3144,13 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>0</v>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -3171,13 +3171,13 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="n">
+      <c r="B101" s="3" t="n">
         <v>-1e-06</v>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D101" s="3" t="n">
         <v>1e-06</v>
@@ -3198,13 +3198,13 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>0</v>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -3225,13 +3225,13 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="n">
+      <c r="B103" s="3" t="n">
         <v>-0.006</v>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D103" s="3" t="n">
         <v>0.006</v>
@@ -3252,13 +3252,13 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
+      <c r="B104" s="3" t="n">
         <v>0.004452</v>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D104" s="3" t="n">
         <v>0.017493</v>
@@ -3279,13 +3279,13 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>0</v>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="n">
+      <c r="B106" s="3" t="n">
         <v>-0.02425</v>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.035778</v>
@@ -3333,13 +3333,13 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>0</v>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D107" s="3" t="n">
         <v>0.077317</v>
@@ -3360,13 +3360,13 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>0</v>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>0</v>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -3414,13 +3414,13 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>0</v>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3441,13 +3441,13 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>0</v>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -3468,13 +3468,13 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>0</v>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -3495,13 +3495,13 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>0</v>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -3522,13 +3522,13 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>0</v>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -3549,13 +3549,13 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>0</v>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -3576,13 +3576,13 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>0</v>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -3603,13 +3603,13 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>0</v>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -3630,13 +3630,13 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>0</v>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -3694,13 +3694,13 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>0</v>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -3721,13 +3721,13 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>0</v>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -3748,13 +3748,13 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>0</v>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -3775,13 +3775,13 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>0</v>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -3802,13 +3802,13 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>0</v>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3829,13 +3829,13 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>0</v>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3856,13 +3856,13 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>0</v>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -3920,13 +3920,13 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>0</v>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D128" s="3" t="n">
         <v>0.105023</v>
@@ -3984,13 +3984,13 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>0</v>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.275751</v>
@@ -4011,13 +4011,13 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>0</v>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -4038,13 +4038,13 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="n">
+      <c r="B132" s="3" t="n">
         <v>0.275751</v>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.069245</v>
@@ -4065,13 +4065,13 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="n">
+      <c r="B133" s="3" t="n">
         <v>0.275751</v>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.344996</v>
@@ -4092,13 +4092,13 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>0</v>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -4731,13 +4731,13 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="5" t="n">
         <v>0.004452</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.017493</v>
@@ -4773,13 +4773,13 @@
           <t>ChangeInWorkingCapital</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="E14" s="5" t="n">
         <v>-0.02425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G14" s="5" t="n">
         <v>-0.035778</v>
@@ -4953,13 +4953,13 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
+      <c r="E18" s="5" t="n">
         <v>0.275751</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G18" s="5" t="n">
         <v>0.344996</v>
@@ -5045,13 +5045,13 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
+      <c r="E20" s="5" t="n">
         <v>-1e-06</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="5" t="n">
         <v>1e-06</v>
@@ -5093,13 +5093,13 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
+      <c r="E21" s="5" t="n">
         <v>-0.006</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.006</v>
@@ -5189,13 +5189,13 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
+      <c r="E23" s="5" t="n">
         <v>-0.022701</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G23" s="5" t="n">
         <v>-0.136589</v>
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
+      <c r="E24" s="5" t="n">
         <v>0.300001</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.105023</v>
@@ -5281,13 +5281,13 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
+      <c r="E25" s="5" t="n">
         <v>0.275751</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G25" s="5" t="n">
         <v>0.069245</v>
@@ -5414,7 +5414,11 @@
           <t>Regulatory and transfer agent</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -6052,10 +6056,10 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.000496</v>
+        <v>0.000496</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-0.0005240000000000001</v>
+        <v>0.0005240000000000001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -6402,7 +6406,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Listing fees 15,750 -</t>
+          <t>Listing fees                                                          15,750                             -</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6450,7 +6454,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Listing fees 15,750 -</t>
+          <t>Listing fees                                                          15,750                             -</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAPL.P.xlsx
+++ b/output/pdf_financials_xlsx/CAPL.P.xlsx
@@ -2947,16 +2947,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.092394</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.092394</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.084855</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.077317</v>
       </c>
     </row>
     <row r="93">
@@ -4368,7 +4368,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CAPL.P.xlsx
+++ b/output/pdf_financials_xlsx/CAPL.P.xlsx
@@ -1302,19 +1302,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.275751</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.344996</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.280248</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.224068</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.14372</v>
       </c>
     </row>
     <row r="35">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.275751</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.344996</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.280248</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.224068</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.14372</v>
       </c>
     </row>
     <row r="37">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.281751</v>
+        <v>0.006</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.344996</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
